--- a/artfynd/A 53363-2022 artfynd.xlsx
+++ b/artfynd/A 53363-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53363-2022 artfynd.xlsx
+++ b/artfynd/A 53363-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>107112067</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477404.7585539488</v>
+        <v>477405</v>
       </c>
       <c r="R2" t="n">
-        <v>7055706.611842213</v>
+        <v>7055707</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107112137</v>
+        <v>107112068</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477560.0884589356</v>
+        <v>477536</v>
       </c>
       <c r="R3" t="n">
-        <v>7055447.611681611</v>
+        <v>7055652</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107112138</v>
+        <v>107112069</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477531.4641039427</v>
+        <v>477534</v>
       </c>
       <c r="R4" t="n">
-        <v>7055429.583046003</v>
+        <v>7055610</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107112126</v>
+        <v>107112070</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477525.8721759706</v>
+        <v>477433</v>
       </c>
       <c r="R5" t="n">
-        <v>7055394.493573721</v>
+        <v>7055546</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107112121</v>
+        <v>107112071</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477506.7800016608</v>
+        <v>477411</v>
       </c>
       <c r="R6" t="n">
-        <v>7055464.886846316</v>
+        <v>7055526</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107112104</v>
+        <v>107112072</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477406.0814757654</v>
+        <v>477429</v>
       </c>
       <c r="R7" t="n">
-        <v>7055704.823884817</v>
+        <v>7055524</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107112117</v>
+        <v>107112074</v>
       </c>
       <c r="B8" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477502.5485816749</v>
+        <v>477443</v>
       </c>
       <c r="R8" t="n">
-        <v>7055496.043275498</v>
+        <v>7055491</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107112072</v>
+        <v>107112075</v>
       </c>
       <c r="B9" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477429.2820145873</v>
+        <v>477505</v>
       </c>
       <c r="R9" t="n">
-        <v>7055524.133005257</v>
+        <v>7055499</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107112124</v>
+        <v>107112076</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477535.3798649331</v>
+        <v>477503</v>
       </c>
       <c r="R10" t="n">
-        <v>7055416.659838526</v>
+        <v>7055453</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,12 +1551,7 @@
         <v>107112077</v>
       </c>
       <c r="B11" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477525.0100635685</v>
+        <v>477525</v>
       </c>
       <c r="R11" t="n">
-        <v>7055398.501757194</v>
+        <v>7055398</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1616,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107112070</v>
+        <v>107112133</v>
       </c>
       <c r="B12" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477432.9989420259</v>
+        <v>477563</v>
       </c>
       <c r="R12" t="n">
-        <v>7055545.894651693</v>
+        <v>7055732</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1713,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107112076</v>
+        <v>107112134</v>
       </c>
       <c r="B13" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477503.1329211274</v>
+        <v>477567</v>
       </c>
       <c r="R13" t="n">
-        <v>7055452.906751771</v>
+        <v>7055654</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1810,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107112118</v>
+        <v>107112135</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477530.8636118677</v>
+        <v>477498</v>
       </c>
       <c r="R14" t="n">
-        <v>7055470.496669282</v>
+        <v>7055524</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,19 +1907,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>107112108</v>
+        <v>107112136</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477618.8960323695</v>
+        <v>477585</v>
       </c>
       <c r="R15" t="n">
-        <v>7055641.509534359</v>
+        <v>7055495</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,19 +2004,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107112113</v>
+        <v>107112137</v>
       </c>
       <c r="B16" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477452.2075505896</v>
+        <v>477560</v>
       </c>
       <c r="R16" t="n">
-        <v>7055617.346403394</v>
+        <v>7055448</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,19 +2101,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>107112119</v>
+        <v>107112138</v>
       </c>
       <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477495.734390176</v>
+        <v>477531</v>
       </c>
       <c r="R17" t="n">
-        <v>7055476.971182949</v>
+        <v>7055429</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,19 +2198,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107112127</v>
+        <v>107112102</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477522.7743878288</v>
+        <v>477405</v>
       </c>
       <c r="R18" t="n">
-        <v>7055397.183587011</v>
+        <v>7055748</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,19 +2295,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>107112039</v>
+        <v>107112103</v>
       </c>
       <c r="B19" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,38 +2335,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nilsslåttern Föllinge S, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477509.3910873273</v>
+        <v>477445</v>
       </c>
       <c r="R19" t="n">
-        <v>7055519.116985272</v>
+        <v>7055750</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,24 +2392,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>107112107</v>
+        <v>107112104</v>
       </c>
       <c r="B20" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477611.8551201055</v>
+        <v>477406</v>
       </c>
       <c r="R20" t="n">
-        <v>7055716.257913383</v>
+        <v>7055705</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2773,19 +2489,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,15 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>107112116</v>
+        <v>107112105</v>
       </c>
       <c r="B21" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2852,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477426.1717684313</v>
+        <v>477406</v>
       </c>
       <c r="R21" t="n">
-        <v>7055525.044468692</v>
+        <v>7055662</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2885,19 +2586,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>107112133</v>
+        <v>107112106</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2940,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477562.5450946799</v>
+        <v>477422</v>
       </c>
       <c r="R22" t="n">
-        <v>7055731.723995223</v>
+        <v>7055661</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2997,19 +2683,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>107112110</v>
+        <v>107112107</v>
       </c>
       <c r="B23" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3076,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477525.4374735313</v>
+        <v>477612</v>
       </c>
       <c r="R23" t="n">
-        <v>7055584.367129061</v>
+        <v>7055716</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3109,19 +2780,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,15 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>107112068</v>
+        <v>107112108</v>
       </c>
       <c r="B24" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3164,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3188,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477536.6048297759</v>
+        <v>477619</v>
       </c>
       <c r="R24" t="n">
-        <v>7055652.318414057</v>
+        <v>7055641</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3221,19 +2877,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,15 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>107112122</v>
+        <v>107112109</v>
       </c>
       <c r="B25" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3300,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477504.0044578151</v>
+        <v>477535</v>
       </c>
       <c r="R25" t="n">
-        <v>7055450.232564858</v>
+        <v>7055652</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3333,19 +2974,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,15 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>107112112</v>
+        <v>107112110</v>
       </c>
       <c r="B26" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3412,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477523.9529894217</v>
+        <v>477526</v>
       </c>
       <c r="R26" t="n">
-        <v>7055626.174316422</v>
+        <v>7055584</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3445,19 +3071,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3484,15 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>107112102</v>
+        <v>107112111</v>
       </c>
       <c r="B27" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3524,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477405.4953640634</v>
+        <v>477537</v>
       </c>
       <c r="R27" t="n">
-        <v>7055747.512416334</v>
+        <v>7055609</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3557,19 +3168,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3596,15 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>107112135</v>
+        <v>107112112</v>
       </c>
       <c r="B28" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3612,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3636,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477498.2951514429</v>
+        <v>477524</v>
       </c>
       <c r="R28" t="n">
-        <v>7055524.086966835</v>
+        <v>7055626</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3669,19 +3265,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3708,15 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>107112041</v>
+        <v>107112113</v>
       </c>
       <c r="B29" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3724,38 +3305,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nilsslåttern Föllinge S, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477516.4363721663</v>
+        <v>477452</v>
       </c>
       <c r="R29" t="n">
-        <v>7055445.253015221</v>
+        <v>7055617</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3785,24 +3362,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3829,15 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>107112123</v>
+        <v>107112114</v>
       </c>
       <c r="B30" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3869,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477531.498774925</v>
+        <v>477439</v>
       </c>
       <c r="R30" t="n">
-        <v>7055434.47416525</v>
+        <v>7055613</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3902,19 +3459,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3941,15 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>107112038</v>
+        <v>107112115</v>
       </c>
       <c r="B31" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3957,42 +3499,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Nilsslåttern Föllinge S, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477482.6016969394</v>
+        <v>477411</v>
       </c>
       <c r="R31" t="n">
-        <v>7055508.635393227</v>
+        <v>7055525</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4022,24 +3556,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4066,15 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>107112134</v>
+        <v>107112116</v>
       </c>
       <c r="B32" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4082,21 +3596,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4106,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477566.4463293387</v>
+        <v>477426</v>
       </c>
       <c r="R32" t="n">
-        <v>7055653.88560549</v>
+        <v>7055525</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4139,19 +3653,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4178,15 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>107112111</v>
+        <v>107112117</v>
       </c>
       <c r="B33" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4218,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477537.1895849766</v>
+        <v>477503</v>
       </c>
       <c r="R33" t="n">
-        <v>7055609.184021487</v>
+        <v>7055496</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4251,19 +3750,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4290,15 +3779,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>107112106</v>
+        <v>107112118</v>
       </c>
       <c r="B34" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477421.3530807599</v>
+        <v>477531</v>
       </c>
       <c r="R34" t="n">
-        <v>7055661.14085223</v>
+        <v>7055470</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4363,19 +3847,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4402,15 +3876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>107112075</v>
+        <v>107112119</v>
       </c>
       <c r="B35" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4418,21 +3887,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4442,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477504.3515901188</v>
+        <v>477496</v>
       </c>
       <c r="R35" t="n">
-        <v>7055499.143101555</v>
+        <v>7055477</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4475,19 +3944,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4514,15 +3973,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>107112109</v>
+        <v>107112120</v>
       </c>
       <c r="B36" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4554,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477534.8239992961</v>
+        <v>477497</v>
       </c>
       <c r="R36" t="n">
-        <v>7055652.331036292</v>
+        <v>7055468</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4587,19 +4041,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4626,15 +4070,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>107112120</v>
+        <v>107112121</v>
       </c>
       <c r="B37" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>477497.006951978</v>
+        <v>477507</v>
       </c>
       <c r="R37" t="n">
-        <v>7055468.068868866</v>
+        <v>7055465</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4699,19 +4138,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4738,15 +4167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>107112069</v>
+        <v>107112122</v>
       </c>
       <c r="B38" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4754,21 +4178,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4778,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>477534.0825439893</v>
+        <v>477504</v>
       </c>
       <c r="R38" t="n">
-        <v>7055610.539977368</v>
+        <v>7055450</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4811,19 +4235,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4850,15 +4264,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>107112136</v>
+        <v>107112123</v>
       </c>
       <c r="B39" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4866,21 +4275,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4890,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477584.4676857276</v>
+        <v>477531</v>
       </c>
       <c r="R39" t="n">
-        <v>7055495.018222877</v>
+        <v>7055434</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4923,19 +4332,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4962,15 +4361,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>107112040</v>
+        <v>107112124</v>
       </c>
       <c r="B40" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4978,42 +4372,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Nilsslåttern Föllinge S, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477517.4146231763</v>
+        <v>477536</v>
       </c>
       <c r="R40" t="n">
-        <v>7055520.394034193</v>
+        <v>7055416</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5043,24 +4429,9 @@
           <t>2023-03-03</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-03-03</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5084,6 +4455,1040 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>107112126</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Nilsslåttern Föllinge S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>477526</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7055394</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>107112127</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Nilsslåttern Föllinge S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>477523</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7055397</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>107112038</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Nilsslåttern Föllinge S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>477482</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7055509</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>107112039</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Nilsslåttern Föllinge S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>477509</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7055519</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>107112040</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Nilsslåttern Föllinge S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>477517</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7055520</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>107112041</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Nilsslåttern Föllinge S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>477516</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7055445</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120520349</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sundkälsbäcken, Sundkälsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>478000</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7055934</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120520362</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sundkälsbäcken, Sundkälsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>478013</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7055890</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120520387</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Sundkälsbäcken, Sundkälsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>478032</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7055851</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120520417</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Juvelbrännan, Juvelbrännan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>478063</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7055771</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53363-2022 artfynd.xlsx
+++ b/artfynd/A 53363-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112067</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112068</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112069</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112070</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112071</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112072</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112074</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112075</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112076</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112077</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112133</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112134</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112135</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112136</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112137</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112138</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112102</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112103</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112104</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112105</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112106</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112107</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112108</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112109</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112110</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112111</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112112</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112113</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112114</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112115</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112116</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112117</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112118</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112119</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112120</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112121</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112122</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112123</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112124</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112126</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4649,6 +4854,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112127</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4759,6 +4969,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112038</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4865,6 +5080,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112039</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4975,6 +5195,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112040</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5081,6 +5306,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112041</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5183,6 +5413,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120520349</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5285,6 +5520,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120520362</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5387,6 +5627,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120520387</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5489,8 +5734,64 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120520417</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>